--- a/Smaers_etal_2013/Smaers_etal_2013_registry_rows.xlsx
+++ b/Smaers_etal_2013/Smaers_etal_2013_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R35f36ca889f14f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R73eee03bcd674654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rc669bf4f2df04658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rd69844115e9d4adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rb5c72f49526b462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R8ab7b4ca2be54d84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -350,13 +350,13 @@
         <x:v>Francesca Hicks dissertation: Table 1 note, Behavioural Data and References (local final draft). Smaers_etal_2018_Figure2-data1.README.md and existing volume inputs.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Previously identified item; full text not obtained for independent re-verification</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 3 / printed p. 61. Individual and hemisphere-specific PCH, FM and PF volumes. PCH measured for this study; FM/PF from earlier work. Existing item number now independently verified.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3727226183/Smaers-2013-Laterality and the evolution of th.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -527,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Fran: cited as play source; papers concern anatomy. Planned folder: Smaers_etal_2013. Target: Volumetric data (mL) used in the current analysis. Table 1: 29 individuals from 16 species. Frontal values reuse earlier work; assess posterior cerebellar contribution against Smaers 2018 and the current merge. Distinct from Smaers–Soligo 2013. Keep hemisphere and specimen IDs.
-Item check 2026-10-25: Previously identified item; full text not obtained for independent re-verification. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Verified in EndNote full text — PDF p. 3 / printed p. 61. Individual and hemisphere-specific PCH, FM and PF volumes. PCH measured for this study; FM/PF from earlier work. Existing item number now independently verified. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3727226183/Smaers-2013-Laterality and the evolution of th.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — anatomy overlap review; not play extraction</x:v>
@@ -707,7 +707,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -991,13 +991,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D93059C-BA91-435E-A060-11DAC75E641E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47DB49BE-60D7-43F4-9CC2-75936100FA83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FA00B7-0373-4C44-B1DF-E2EFD4CB31A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D007A461-6F67-45EF-8842-D61C7FEFA769}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51ECC354-7291-4D37-B90F-CED6B200DE75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8424538-1ACC-4153-B2D2-91E2005FB014}"/>
 </file>